--- a/Figure_Source_Data/SourceData_EDFig4.xlsx
+++ b/Figure_Source_Data/SourceData_EDFig4.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -38,16 +38,15 @@
     <t xml:space="preserve">BAU</t>
   </si>
   <si>
-    <t xml:space="preserve">BNP</t>
-  </si>
-  <si>
     <t xml:space="preserve">BNPR</t>
   </si>
   <si>
-    <t xml:space="preserve">BNPRLopt</t>
+    <t xml:space="preserve">BNPRL
+opt</t>
   </si>
   <si>
-    <t xml:space="preserve">BNPRLopt(dep)</t>
+    <t xml:space="preserve">BNPRL
+opt(dep)</t>
   </si>
   <si>
     <t xml:space="preserve">QY024</t>
@@ -209,7 +208,7 @@
     <t xml:space="preserve">QY310</t>
   </si>
   <si>
-    <t xml:space="preserve">mean_manure</t>
+    <t xml:space="preserve">max_manure</t>
   </si>
   <si>
     <t xml:space="preserve">ratio</t>
@@ -218,7 +217,7 @@
     <t xml:space="preserve">dep</t>
   </si>
   <si>
-    <t xml:space="preserve">mean_dep</t>
+    <t xml:space="preserve">max_dep</t>
   </si>
 </sst>
 </file>
@@ -594,7 +593,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>4.264872523</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -608,7 +607,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3.406499365</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -619,35 +618,35 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>3.406499365</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>4.02876</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -656,12 +655,12 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
         <v>4.02876</v>
@@ -670,7 +669,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -678,13 +677,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3.734775373</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -692,97 +691,97 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>4.02876</v>
+        <v>3.734775373</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3.734775373</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.734775373</v>
+        <v>2.686835045</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3.734775373</v>
+        <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.81542</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="n">
-        <v>2.686835045</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.68004133</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -796,7 +795,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -804,13 +803,13 @@
         <v>14</v>
       </c>
       <c r="B19" t="n">
-        <v>2.81542</v>
+        <v>3.1217</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -824,7 +823,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -832,13 +831,13 @@
         <v>14</v>
       </c>
       <c r="B21" t="n">
-        <v>1.68004133</v>
+        <v>3.1217</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -849,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
@@ -860,10 +859,10 @@
         <v>15</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3.7014</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -874,10 +873,10 @@
         <v>15</v>
       </c>
       <c r="B24" t="n">
-        <v>3.1217</v>
+        <v>0.486131393</v>
       </c>
       <c r="C24" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
@@ -888,10 +887,10 @@
         <v>15</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>3.7014</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
@@ -899,16 +898,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B26" t="n">
-        <v>3.1217</v>
+        <v>7.581995597</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -916,13 +915,13 @@
         <v>16</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1.452307692</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -933,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -944,41 +943,41 @@
         <v>16</v>
       </c>
       <c r="B29" t="n">
-        <v>3.7014</v>
+        <v>1.452307692</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B30" t="n">
-        <v>0.486131393</v>
+        <v>0</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B31" t="n">
-        <v>3.7014</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -986,13 +985,13 @@
         <v>17</v>
       </c>
       <c r="B32" t="n">
-        <v>7.581995597</v>
+        <v>0</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1000,55 +999,55 @@
         <v>17</v>
       </c>
       <c r="B33" t="n">
-        <v>1.452307692</v>
+        <v>0</v>
       </c>
       <c r="C33" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34" t="n">
-        <v>1.452307692</v>
+        <v>0</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1.8259</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
       </c>
       <c r="D35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B36" t="n">
-        <v>1.452307692</v>
+        <v>0</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -1056,74 +1055,74 @@
         <v>18</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1.8259</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
@@ -1137,7 +1136,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
@@ -1151,10 +1150,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44" t="n">
-        <v>1.8259</v>
+        <v>0</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -1165,7 +1164,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
@@ -1179,147 +1178,147 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B46" t="n">
-        <v>1.8259</v>
+        <v>4.264872523</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D47" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D48" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>1.488</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1.488</v>
       </c>
       <c r="C53" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>1.895498899</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
       </c>
       <c r="D54" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>1.895498899</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B56" t="n">
         <v>0</v>
@@ -1328,26 +1327,26 @@
         <v>5</v>
       </c>
       <c r="D56" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B57" t="n">
-        <v>4.264872523</v>
+        <v>1.895498899</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
       </c>
       <c r="D57" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B58" t="n">
         <v>0</v>
@@ -1356,26 +1355,26 @@
         <v>5</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>1.4136</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
       </c>
       <c r="D59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B60" t="n">
         <v>0</v>
@@ -1384,32 +1383,32 @@
         <v>5</v>
       </c>
       <c r="D60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>1.4136</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
       </c>
       <c r="D61" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D62" t="s">
         <v>6</v>
@@ -1417,13 +1416,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>1.178</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -1431,13 +1430,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B64" t="n">
-        <v>1.488</v>
+        <v>0.478018506</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D64" t="s">
         <v>8</v>
@@ -1445,13 +1444,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>1.178</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D65" t="s">
         <v>9</v>
@@ -1459,237 +1458,237 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B66" t="n">
-        <v>1.488</v>
+        <v>0.638526112</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B67" t="n">
-        <v>1.895498899</v>
+        <v>0.19875</v>
       </c>
       <c r="C67" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B68" t="n">
-        <v>1.895498899</v>
+        <v>0</v>
       </c>
       <c r="C68" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B69" t="n">
-        <v>1.895498899</v>
+        <v>0.19875</v>
       </c>
       <c r="C69" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B71" t="n">
-        <v>1.895498899</v>
+        <v>0.744</v>
       </c>
       <c r="C71" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>0.744</v>
       </c>
       <c r="C73" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B74" t="n">
-        <v>1.4136</v>
+        <v>0</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
       </c>
       <c r="D74" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>2.4149</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B76" t="n">
-        <v>1.4136</v>
+        <v>0</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>1.632916742</v>
       </c>
       <c r="C77" t="s">
         <v>5</v>
       </c>
       <c r="D77" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B78" t="n">
         <v>0</v>
       </c>
       <c r="C78" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B79" t="n">
-        <v>1.178</v>
+        <v>1.2896</v>
       </c>
       <c r="C79" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B80" t="n">
-        <v>0.478018506</v>
+        <v>0</v>
       </c>
       <c r="C80" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B81" t="n">
-        <v>1.178</v>
+        <v>0.738042031</v>
       </c>
       <c r="C81" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B82" t="n">
-        <v>0.638526112</v>
+        <v>0</v>
       </c>
       <c r="C82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D82" t="s">
         <v>6</v>
@@ -1697,13 +1696,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B83" t="n">
-        <v>0.19875</v>
+        <v>2.9636</v>
       </c>
       <c r="C83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -1711,13 +1710,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B84" t="n">
-        <v>0.19875</v>
+        <v>0</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D84" t="s">
         <v>8</v>
@@ -1725,13 +1724,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>2.765415861</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
@@ -1739,237 +1738,237 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B86" t="n">
-        <v>0.19875</v>
+        <v>0.638526112</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D86" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>0.638526112</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D87" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B88" t="n">
         <v>0</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D88" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B89" t="n">
-        <v>0.744</v>
+        <v>0.638526112</v>
       </c>
       <c r="C89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D89" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D90" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B91" t="n">
-        <v>0.744</v>
+        <v>5.2824</v>
       </c>
       <c r="C91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
       </c>
       <c r="C92" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>3.670291708</v>
       </c>
       <c r="C93" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B94" t="n">
-        <v>2.4149</v>
+        <v>0</v>
       </c>
       <c r="C94" t="s">
         <v>5</v>
       </c>
       <c r="D94" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>3.91685</v>
       </c>
       <c r="C95" t="s">
         <v>5</v>
       </c>
       <c r="D95" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B96" t="n">
-        <v>1.632916742</v>
+        <v>0</v>
       </c>
       <c r="C96" t="s">
         <v>5</v>
       </c>
       <c r="D96" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>2.237728262</v>
       </c>
       <c r="C97" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D97" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
       </c>
       <c r="C98" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D98" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B99" t="n">
-        <v>1.2896</v>
+        <v>1.8848</v>
       </c>
       <c r="C99" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D99" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
       </c>
       <c r="C100" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B101" t="n">
-        <v>0.738042031</v>
+        <v>1.8848</v>
       </c>
       <c r="C101" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D101" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D102" t="s">
         <v>6</v>
@@ -1977,13 +1976,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>1.22512</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -1991,13 +1990,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B104" t="n">
-        <v>2.9636</v>
+        <v>0</v>
       </c>
       <c r="C104" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D104" t="s">
         <v>8</v>
@@ -2005,13 +2004,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>1.204466225</v>
       </c>
       <c r="C105" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D105" t="s">
         <v>9</v>
@@ -2019,175 +2018,175 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B106" t="n">
-        <v>2.765415861</v>
+        <v>0</v>
       </c>
       <c r="C106" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D106" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B107" t="n">
-        <v>0.638526112</v>
+        <v>2.81542</v>
       </c>
       <c r="C107" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D107" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B108" t="n">
-        <v>0.638526112</v>
+        <v>2.81542</v>
       </c>
       <c r="C108" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D108" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B109" t="n">
-        <v>0.638526112</v>
+        <v>2.81542</v>
       </c>
       <c r="C109" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D109" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
       </c>
       <c r="C110" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D110" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B111" t="n">
-        <v>0.638526112</v>
+        <v>2.4738</v>
       </c>
       <c r="C111" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D111" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B112" t="n">
-        <v>0</v>
+        <v>0.050352176</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D112" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>2.4738</v>
       </c>
       <c r="C113" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B114" t="n">
-        <v>5.2824</v>
+        <v>0</v>
       </c>
       <c r="C114" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D114" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>2.81542</v>
       </c>
       <c r="C115" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D115" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B116" t="n">
-        <v>3.670291708</v>
+        <v>0</v>
       </c>
       <c r="C116" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D116" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>1.326072235</v>
       </c>
       <c r="C117" t="s">
         <v>5</v>
       </c>
       <c r="D117" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -2196,26 +2195,26 @@
         <v>5</v>
       </c>
       <c r="D118" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B119" t="n">
-        <v>3.91685</v>
+        <v>1.61386</v>
       </c>
       <c r="C119" t="s">
         <v>5</v>
       </c>
       <c r="D119" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -2224,32 +2223,32 @@
         <v>5</v>
       </c>
       <c r="D120" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B121" t="n">
-        <v>2.237728262</v>
+        <v>1.10944514</v>
       </c>
       <c r="C121" t="s">
         <v>5</v>
       </c>
       <c r="D121" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>0.56222425</v>
       </c>
       <c r="C122" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D122" t="s">
         <v>6</v>
@@ -2257,13 +2256,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>0.56222425</v>
       </c>
       <c r="C123" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -2271,13 +2270,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B124" t="n">
-        <v>1.8848</v>
+        <v>0.478793026</v>
       </c>
       <c r="C124" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
@@ -2285,13 +2284,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>0.56222425</v>
       </c>
       <c r="C125" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
@@ -2299,21 +2298,21 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B126" t="n">
-        <v>1.8848</v>
+        <v>4.979700498</v>
       </c>
       <c r="C126" t="s">
         <v>5</v>
       </c>
       <c r="D126" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2322,12 +2321,12 @@
         <v>5</v>
       </c>
       <c r="D127" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2336,138 +2335,138 @@
         <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B129" t="n">
-        <v>1.22512</v>
+        <v>0</v>
       </c>
       <c r="C129" t="s">
         <v>5</v>
       </c>
       <c r="D129" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>0.56222425</v>
       </c>
       <c r="C130" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D130" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B131" t="n">
-        <v>1.204466225</v>
+        <v>0.56222425</v>
       </c>
       <c r="C131" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D131" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>0.447414094</v>
       </c>
       <c r="C132" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D132" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>0.56222425</v>
       </c>
       <c r="C133" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D133" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B134" t="n">
-        <v>2.81542</v>
+        <v>0</v>
       </c>
       <c r="C134" t="s">
         <v>5</v>
       </c>
       <c r="D134" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B135" t="n">
-        <v>2.81542</v>
+        <v>3.36908</v>
       </c>
       <c r="C135" t="s">
         <v>5</v>
       </c>
       <c r="D135" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B136" t="n">
-        <v>2.81542</v>
+        <v>1.573218298</v>
       </c>
       <c r="C136" t="s">
         <v>5</v>
       </c>
       <c r="D136" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>3.36908</v>
       </c>
       <c r="C137" t="s">
         <v>5</v>
       </c>
       <c r="D137" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2476,54 +2475,54 @@
         <v>5</v>
       </c>
       <c r="D138" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B139" t="n">
-        <v>2.4738</v>
+        <v>0.73625</v>
       </c>
       <c r="C139" t="s">
         <v>5</v>
       </c>
       <c r="D139" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B140" t="n">
-        <v>0.050352176</v>
+        <v>0.73625</v>
       </c>
       <c r="C140" t="s">
         <v>5</v>
       </c>
       <c r="D140" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B141" t="n">
-        <v>2.4738</v>
+        <v>0.73625</v>
       </c>
       <c r="C141" t="s">
         <v>5</v>
       </c>
       <c r="D141" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B142" t="n">
         <v>0</v>
@@ -2537,10 +2536,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>0.2945</v>
       </c>
       <c r="C143" t="s">
         <v>5</v>
@@ -2551,10 +2550,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B144" t="n">
-        <v>2.81542</v>
+        <v>0</v>
       </c>
       <c r="C144" t="s">
         <v>5</v>
@@ -2565,10 +2564,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>0.2945</v>
       </c>
       <c r="C145" t="s">
         <v>5</v>
@@ -2579,63 +2578,63 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B146" t="n">
-        <v>1.326072235</v>
+        <v>0</v>
       </c>
       <c r="C146" t="s">
         <v>5</v>
       </c>
       <c r="D146" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>1.8848</v>
       </c>
       <c r="C147" t="s">
         <v>5</v>
       </c>
       <c r="D147" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>1.047123835</v>
       </c>
       <c r="C148" t="s">
         <v>5</v>
       </c>
       <c r="D148" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B149" t="n">
-        <v>1.61386</v>
+        <v>1.8848</v>
       </c>
       <c r="C149" t="s">
         <v>5</v>
       </c>
       <c r="D149" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B150" t="n">
         <v>0</v>
@@ -2644,110 +2643,110 @@
         <v>5</v>
       </c>
       <c r="D150" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B151" t="n">
-        <v>1.10944514</v>
+        <v>3.51633</v>
       </c>
       <c r="C151" t="s">
         <v>5</v>
       </c>
       <c r="D151" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B152" t="n">
-        <v>0.56222425</v>
+        <v>3.341869482</v>
       </c>
       <c r="C152" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D152" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B153" t="n">
-        <v>0.56222425</v>
+        <v>3.51633</v>
       </c>
       <c r="C153" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D153" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B154" t="n">
-        <v>0.56222425</v>
+        <v>0</v>
       </c>
       <c r="C154" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D154" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B155" t="n">
-        <v>0.478793026</v>
+        <v>0.558</v>
       </c>
       <c r="C155" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D155" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B156" t="n">
-        <v>0.56222425</v>
+        <v>0</v>
       </c>
       <c r="C156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D156" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B157" t="n">
-        <v>4.979700498</v>
+        <v>0.558</v>
       </c>
       <c r="C157" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D157" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B158" t="n">
         <v>0</v>
@@ -2756,60 +2755,60 @@
         <v>5</v>
       </c>
       <c r="D158" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>3.1217</v>
       </c>
       <c r="C159" t="s">
         <v>5</v>
       </c>
       <c r="D159" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>0.785543048</v>
       </c>
       <c r="C160" t="s">
         <v>5</v>
       </c>
       <c r="D160" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>3.1217</v>
       </c>
       <c r="C161" t="s">
         <v>5</v>
       </c>
       <c r="D161" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B162" t="n">
-        <v>0.56222425</v>
+        <v>0</v>
       </c>
       <c r="C162" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D162" t="s">
         <v>6</v>
@@ -2817,13 +2816,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B163" t="n">
-        <v>0.56222425</v>
+        <v>1.8848</v>
       </c>
       <c r="C163" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -2831,13 +2830,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B164" t="n">
-        <v>0.56222425</v>
+        <v>0</v>
       </c>
       <c r="C164" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D164" t="s">
         <v>8</v>
@@ -2845,13 +2844,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B165" t="n">
-        <v>0.447414094</v>
+        <v>1.8848</v>
       </c>
       <c r="C165" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
@@ -2859,175 +2858,175 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B166" t="n">
-        <v>0.56222425</v>
+        <v>0</v>
       </c>
       <c r="C166" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D166" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>0.61845</v>
       </c>
       <c r="C167" t="s">
         <v>5</v>
       </c>
       <c r="D167" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>0.61845</v>
       </c>
       <c r="C168" t="s">
         <v>5</v>
       </c>
       <c r="D168" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B169" t="n">
-        <v>3.36908</v>
+        <v>0.61845</v>
       </c>
       <c r="C169" t="s">
         <v>5</v>
       </c>
       <c r="D169" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B170" t="n">
-        <v>1.573218298</v>
+        <v>1.509973699</v>
       </c>
       <c r="C170" t="s">
         <v>5</v>
       </c>
       <c r="D170" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B171" t="n">
-        <v>3.36908</v>
+        <v>1.509973699</v>
       </c>
       <c r="C171" t="s">
         <v>5</v>
       </c>
       <c r="D171" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>0.634661258</v>
       </c>
       <c r="C172" t="s">
         <v>5</v>
       </c>
       <c r="D172" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>1.509973699</v>
       </c>
       <c r="C173" t="s">
         <v>5</v>
       </c>
       <c r="D173" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B174" t="n">
-        <v>0.73625</v>
+        <v>0</v>
       </c>
       <c r="C174" t="s">
         <v>5</v>
       </c>
       <c r="D174" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B175" t="n">
-        <v>0.73625</v>
+        <v>2.4149</v>
       </c>
       <c r="C175" t="s">
         <v>5</v>
       </c>
       <c r="D175" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B176" t="n">
-        <v>0.73625</v>
+        <v>2.045798143</v>
       </c>
       <c r="C176" t="s">
         <v>5</v>
       </c>
       <c r="D176" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>2.4149</v>
       </c>
       <c r="C177" t="s">
         <v>5</v>
       </c>
       <c r="D177" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B178" t="n">
         <v>0</v>
@@ -3036,60 +3035,60 @@
         <v>5</v>
       </c>
       <c r="D178" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B179" t="n">
-        <v>0.2945</v>
+        <v>2.4149</v>
       </c>
       <c r="C179" t="s">
         <v>5</v>
       </c>
       <c r="D179" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B180" t="n">
-        <v>0</v>
+        <v>0.852471425</v>
       </c>
       <c r="C180" t="s">
         <v>5</v>
       </c>
       <c r="D180" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B181" t="n">
-        <v>0.2945</v>
+        <v>2.4149</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
       </c>
       <c r="D181" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B182" t="n">
         <v>0</v>
       </c>
       <c r="C182" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D182" t="s">
         <v>6</v>
@@ -3097,13 +3096,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>4.4392</v>
       </c>
       <c r="C183" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -3111,13 +3110,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B184" t="n">
-        <v>1.8848</v>
+        <v>0</v>
       </c>
       <c r="C184" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D184" t="s">
         <v>8</v>
@@ -3125,13 +3124,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B185" t="n">
-        <v>1.047123835</v>
+        <v>2.210310245</v>
       </c>
       <c r="C185" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D185" t="s">
         <v>9</v>
@@ -3139,175 +3138,175 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B186" t="n">
-        <v>1.8848</v>
+        <v>0</v>
       </c>
       <c r="C186" t="s">
         <v>5</v>
       </c>
       <c r="D186" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>0.4123</v>
       </c>
       <c r="C187" t="s">
         <v>5</v>
       </c>
       <c r="D187" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>0.4123</v>
       </c>
       <c r="C188" t="s">
         <v>5</v>
       </c>
       <c r="D188" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B189" t="n">
-        <v>3.51633</v>
+        <v>0.4123</v>
       </c>
       <c r="C189" t="s">
         <v>5</v>
       </c>
       <c r="D189" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B190" t="n">
-        <v>3.341869482</v>
+        <v>0</v>
       </c>
       <c r="C190" t="s">
         <v>5</v>
       </c>
       <c r="D190" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B191" t="n">
-        <v>3.51633</v>
+        <v>0</v>
       </c>
       <c r="C191" t="s">
         <v>5</v>
       </c>
       <c r="D191" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B192" t="n">
         <v>0</v>
       </c>
       <c r="C192" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D192" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B193" t="n">
         <v>0</v>
       </c>
       <c r="C193" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D193" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B194" t="n">
-        <v>0.558</v>
+        <v>0</v>
       </c>
       <c r="C194" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D194" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>2.604</v>
       </c>
       <c r="C195" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D195" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B196" t="n">
-        <v>0.558</v>
+        <v>1.727042339</v>
       </c>
       <c r="C196" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D196" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
+        <v>2.604</v>
       </c>
       <c r="C197" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D197" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B198" t="n">
         <v>0</v>
@@ -3316,60 +3315,60 @@
         <v>5</v>
       </c>
       <c r="D198" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B199" t="n">
-        <v>3.1217</v>
+        <v>1.178</v>
       </c>
       <c r="C199" t="s">
         <v>5</v>
       </c>
       <c r="D199" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B200" t="n">
-        <v>0.785543048</v>
+        <v>0.886192898</v>
       </c>
       <c r="C200" t="s">
         <v>5</v>
       </c>
       <c r="D200" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B201" t="n">
-        <v>3.1217</v>
+        <v>1.178</v>
       </c>
       <c r="C201" t="s">
         <v>5</v>
       </c>
       <c r="D201" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B202" t="n">
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D202" t="s">
         <v>6</v>
@@ -3377,13 +3376,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>0.992</v>
       </c>
       <c r="C203" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -3391,13 +3390,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B204" t="n">
-        <v>1.8848</v>
+        <v>0.992</v>
       </c>
       <c r="C204" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D204" t="s">
         <v>8</v>
@@ -3405,13 +3404,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B205" t="n">
-        <v>0</v>
+        <v>0.992</v>
       </c>
       <c r="C205" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D205" t="s">
         <v>9</v>
@@ -3419,35 +3418,35 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B206" t="n">
-        <v>1.8848</v>
+        <v>0</v>
       </c>
       <c r="C206" t="s">
         <v>5</v>
       </c>
       <c r="D206" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B207" t="n">
-        <v>0</v>
+        <v>2.81542</v>
       </c>
       <c r="C207" t="s">
         <v>5</v>
       </c>
       <c r="D207" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B208" t="n">
         <v>0</v>
@@ -3456,819 +3455,77 @@
         <v>5</v>
       </c>
       <c r="D208" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B209" t="n">
-        <v>0.61845</v>
+        <v>1.885925644</v>
       </c>
       <c r="C209" t="s">
         <v>5</v>
       </c>
       <c r="D209" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B210" t="n">
-        <v>0.61845</v>
+        <v>0</v>
       </c>
       <c r="C210" t="s">
         <v>5</v>
       </c>
       <c r="D210" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B211" t="n">
-        <v>0.61845</v>
+        <v>2.4149</v>
       </c>
       <c r="C211" t="s">
         <v>5</v>
       </c>
       <c r="D211" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B212" t="n">
-        <v>1.509973699</v>
+        <v>0</v>
       </c>
       <c r="C212" t="s">
         <v>5</v>
       </c>
       <c r="D212" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B213" t="n">
-        <v>1.509973699</v>
+        <v>2.4149</v>
       </c>
       <c r="C213" t="s">
         <v>5</v>
       </c>
       <c r="D213" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="s">
-        <v>53</v>
-      </c>
-      <c r="B214" t="n">
-        <v>1.509973699</v>
-      </c>
-      <c r="C214" t="s">
-        <v>5</v>
-      </c>
-      <c r="D214" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="s">
-        <v>53</v>
-      </c>
-      <c r="B215" t="n">
-        <v>0.634661258</v>
-      </c>
-      <c r="C215" t="s">
-        <v>5</v>
-      </c>
-      <c r="D215" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="s">
-        <v>53</v>
-      </c>
-      <c r="B216" t="n">
-        <v>1.509973699</v>
-      </c>
-      <c r="C216" t="s">
-        <v>5</v>
-      </c>
-      <c r="D216" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="s">
-        <v>54</v>
-      </c>
-      <c r="B217" t="n">
-        <v>0</v>
-      </c>
-      <c r="C217" t="s">
-        <v>5</v>
-      </c>
-      <c r="D217" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="s">
-        <v>54</v>
-      </c>
-      <c r="B218" t="n">
-        <v>0</v>
-      </c>
-      <c r="C218" t="s">
-        <v>5</v>
-      </c>
-      <c r="D218" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="s">
-        <v>54</v>
-      </c>
-      <c r="B219" t="n">
-        <v>2.4149</v>
-      </c>
-      <c r="C219" t="s">
-        <v>5</v>
-      </c>
-      <c r="D219" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="s">
-        <v>54</v>
-      </c>
-      <c r="B220" t="n">
-        <v>2.045798143</v>
-      </c>
-      <c r="C220" t="s">
-        <v>5</v>
-      </c>
-      <c r="D220" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="s">
-        <v>54</v>
-      </c>
-      <c r="B221" t="n">
-        <v>2.4149</v>
-      </c>
-      <c r="C221" t="s">
-        <v>5</v>
-      </c>
-      <c r="D221" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="s">
-        <v>55</v>
-      </c>
-      <c r="B222" t="n">
-        <v>0</v>
-      </c>
-      <c r="C222" t="s">
-        <v>5</v>
-      </c>
-      <c r="D222" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="s">
-        <v>55</v>
-      </c>
-      <c r="B223" t="n">
-        <v>0</v>
-      </c>
-      <c r="C223" t="s">
-        <v>5</v>
-      </c>
-      <c r="D223" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="s">
-        <v>55</v>
-      </c>
-      <c r="B224" t="n">
-        <v>2.4149</v>
-      </c>
-      <c r="C224" t="s">
-        <v>5</v>
-      </c>
-      <c r="D224" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="s">
-        <v>55</v>
-      </c>
-      <c r="B225" t="n">
-        <v>0.852471425</v>
-      </c>
-      <c r="C225" t="s">
-        <v>5</v>
-      </c>
-      <c r="D225" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="s">
-        <v>55</v>
-      </c>
-      <c r="B226" t="n">
-        <v>2.4149</v>
-      </c>
-      <c r="C226" t="s">
-        <v>5</v>
-      </c>
-      <c r="D226" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s">
-        <v>56</v>
-      </c>
-      <c r="B227" t="n">
-        <v>0</v>
-      </c>
-      <c r="C227" t="s">
-        <v>13</v>
-      </c>
-      <c r="D227" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="s">
-        <v>56</v>
-      </c>
-      <c r="B228" t="n">
-        <v>0</v>
-      </c>
-      <c r="C228" t="s">
-        <v>13</v>
-      </c>
-      <c r="D228" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="s">
-        <v>56</v>
-      </c>
-      <c r="B229" t="n">
-        <v>4.4392</v>
-      </c>
-      <c r="C229" t="s">
-        <v>13</v>
-      </c>
-      <c r="D229" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="s">
-        <v>56</v>
-      </c>
-      <c r="B230" t="n">
-        <v>0</v>
-      </c>
-      <c r="C230" t="s">
-        <v>13</v>
-      </c>
-      <c r="D230" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="s">
-        <v>56</v>
-      </c>
-      <c r="B231" t="n">
-        <v>2.210310245</v>
-      </c>
-      <c r="C231" t="s">
-        <v>13</v>
-      </c>
-      <c r="D231" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="s">
-        <v>57</v>
-      </c>
-      <c r="B232" t="n">
-        <v>0</v>
-      </c>
-      <c r="C232" t="s">
-        <v>5</v>
-      </c>
-      <c r="D232" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="s">
-        <v>57</v>
-      </c>
-      <c r="B233" t="n">
-        <v>0</v>
-      </c>
-      <c r="C233" t="s">
-        <v>5</v>
-      </c>
-      <c r="D233" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="s">
-        <v>57</v>
-      </c>
-      <c r="B234" t="n">
-        <v>0.4123</v>
-      </c>
-      <c r="C234" t="s">
-        <v>5</v>
-      </c>
-      <c r="D234" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="s">
-        <v>57</v>
-      </c>
-      <c r="B235" t="n">
-        <v>0.4123</v>
-      </c>
-      <c r="C235" t="s">
-        <v>5</v>
-      </c>
-      <c r="D235" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="s">
-        <v>57</v>
-      </c>
-      <c r="B236" t="n">
-        <v>0.4123</v>
-      </c>
-      <c r="C236" t="s">
-        <v>5</v>
-      </c>
-      <c r="D236" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="s">
-        <v>58</v>
-      </c>
-      <c r="B237" t="n">
-        <v>0</v>
-      </c>
-      <c r="C237" t="s">
-        <v>5</v>
-      </c>
-      <c r="D237" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="s">
-        <v>58</v>
-      </c>
-      <c r="B238" t="n">
-        <v>0</v>
-      </c>
-      <c r="C238" t="s">
-        <v>5</v>
-      </c>
-      <c r="D238" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="s">
-        <v>58</v>
-      </c>
-      <c r="B239" t="n">
-        <v>0</v>
-      </c>
-      <c r="C239" t="s">
-        <v>5</v>
-      </c>
-      <c r="D239" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="s">
-        <v>58</v>
-      </c>
-      <c r="B240" t="n">
-        <v>0</v>
-      </c>
-      <c r="C240" t="s">
-        <v>5</v>
-      </c>
-      <c r="D240" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="s">
-        <v>58</v>
-      </c>
-      <c r="B241" t="n">
-        <v>0</v>
-      </c>
-      <c r="C241" t="s">
-        <v>5</v>
-      </c>
-      <c r="D241" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s">
-        <v>59</v>
-      </c>
-      <c r="B242" t="n">
-        <v>0</v>
-      </c>
-      <c r="C242" t="s">
-        <v>13</v>
-      </c>
-      <c r="D242" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s">
-        <v>59</v>
-      </c>
-      <c r="B243" t="n">
-        <v>0</v>
-      </c>
-      <c r="C243" t="s">
-        <v>13</v>
-      </c>
-      <c r="D243" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s">
-        <v>59</v>
-      </c>
-      <c r="B244" t="n">
-        <v>2.604</v>
-      </c>
-      <c r="C244" t="s">
-        <v>13</v>
-      </c>
-      <c r="D244" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="s">
-        <v>59</v>
-      </c>
-      <c r="B245" t="n">
-        <v>1.727042339</v>
-      </c>
-      <c r="C245" t="s">
-        <v>13</v>
-      </c>
-      <c r="D245" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="s">
-        <v>59</v>
-      </c>
-      <c r="B246" t="n">
-        <v>2.604</v>
-      </c>
-      <c r="C246" t="s">
-        <v>13</v>
-      </c>
-      <c r="D246" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="s">
-        <v>60</v>
-      </c>
-      <c r="B247" t="n">
-        <v>0</v>
-      </c>
-      <c r="C247" t="s">
-        <v>5</v>
-      </c>
-      <c r="D247" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="s">
-        <v>60</v>
-      </c>
-      <c r="B248" t="n">
-        <v>0</v>
-      </c>
-      <c r="C248" t="s">
-        <v>5</v>
-      </c>
-      <c r="D248" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s">
-        <v>60</v>
-      </c>
-      <c r="B249" t="n">
-        <v>1.178</v>
-      </c>
-      <c r="C249" t="s">
-        <v>5</v>
-      </c>
-      <c r="D249" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="s">
-        <v>60</v>
-      </c>
-      <c r="B250" t="n">
-        <v>0.886192898</v>
-      </c>
-      <c r="C250" t="s">
-        <v>5</v>
-      </c>
-      <c r="D250" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="s">
-        <v>60</v>
-      </c>
-      <c r="B251" t="n">
-        <v>1.178</v>
-      </c>
-      <c r="C251" t="s">
-        <v>5</v>
-      </c>
-      <c r="D251" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="s">
-        <v>61</v>
-      </c>
-      <c r="B252" t="n">
-        <v>0</v>
-      </c>
-      <c r="C252" t="s">
-        <v>13</v>
-      </c>
-      <c r="D252" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="s">
-        <v>61</v>
-      </c>
-      <c r="B253" t="n">
-        <v>0</v>
-      </c>
-      <c r="C253" t="s">
-        <v>13</v>
-      </c>
-      <c r="D253" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s">
-        <v>61</v>
-      </c>
-      <c r="B254" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="C254" t="s">
-        <v>13</v>
-      </c>
-      <c r="D254" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="s">
-        <v>61</v>
-      </c>
-      <c r="B255" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="C255" t="s">
-        <v>13</v>
-      </c>
-      <c r="D255" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="s">
-        <v>61</v>
-      </c>
-      <c r="B256" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="C256" t="s">
-        <v>13</v>
-      </c>
-      <c r="D256" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="s">
-        <v>62</v>
-      </c>
-      <c r="B257" t="n">
-        <v>0</v>
-      </c>
-      <c r="C257" t="s">
-        <v>5</v>
-      </c>
-      <c r="D257" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="s">
-        <v>62</v>
-      </c>
-      <c r="B258" t="n">
-        <v>0</v>
-      </c>
-      <c r="C258" t="s">
-        <v>5</v>
-      </c>
-      <c r="D258" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="s">
-        <v>62</v>
-      </c>
-      <c r="B259" t="n">
-        <v>2.81542</v>
-      </c>
-      <c r="C259" t="s">
-        <v>5</v>
-      </c>
-      <c r="D259" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>62</v>
-      </c>
-      <c r="B260" t="n">
-        <v>0</v>
-      </c>
-      <c r="C260" t="s">
-        <v>5</v>
-      </c>
-      <c r="D260" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="s">
-        <v>62</v>
-      </c>
-      <c r="B261" t="n">
-        <v>1.885925644</v>
-      </c>
-      <c r="C261" t="s">
-        <v>5</v>
-      </c>
-      <c r="D261" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="s">
-        <v>63</v>
-      </c>
-      <c r="B262" t="n">
-        <v>0</v>
-      </c>
-      <c r="C262" t="s">
-        <v>5</v>
-      </c>
-      <c r="D262" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="s">
-        <v>63</v>
-      </c>
-      <c r="B263" t="n">
-        <v>0</v>
-      </c>
-      <c r="C263" t="s">
-        <v>5</v>
-      </c>
-      <c r="D263" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="s">
-        <v>63</v>
-      </c>
-      <c r="B264" t="n">
-        <v>2.4149</v>
-      </c>
-      <c r="C264" t="s">
-        <v>5</v>
-      </c>
-      <c r="D264" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="s">
-        <v>63</v>
-      </c>
-      <c r="B265" t="n">
-        <v>0</v>
-      </c>
-      <c r="C265" t="s">
-        <v>5</v>
-      </c>
-      <c r="D265" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="s">
-        <v>63</v>
-      </c>
-      <c r="B266" t="n">
-        <v>2.4149</v>
-      </c>
-      <c r="C266" t="s">
-        <v>5</v>
-      </c>
-      <c r="D266" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4284,68 +3541,128 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.862663752069839</v>
+        <v>2.89148145990879</v>
       </c>
       <c r="C2" t="n">
-        <v>0.307867440177241</v>
+        <v>0.351247836161662</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.417323368009011</v>
+        <v>2.89148145990879</v>
       </c>
       <c r="C3" t="n">
-        <v>0.148934363738837</v>
+        <v>0.233396586164216</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>0.574740915826528</v>
+        <v>2.89148145990879</v>
       </c>
       <c r="C4" t="n">
-        <v>0.205113538265731</v>
+        <v>0.893913121855809</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>2.43491367882287</v>
+        <v>2.89148145990879</v>
       </c>
       <c r="C5" t="n">
-        <v>0.868971994653899</v>
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>2.80206231478457</v>
+        <v>2.61270412510975</v>
       </c>
       <c r="C6" t="n">
+        <v>0.206201080695495</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.61270412510975</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.13882934584113</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2.61270412510975</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.81051993246203</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2.61270412510975</v>
+      </c>
+      <c r="C9" t="n">
         <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4364,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4406,7 +3723,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>3.908966064</v>
+        <v>3.406499365</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4420,7 +3737,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3.406499365</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4431,21 +3748,21 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>5.299603939</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
         <v>5.299603939</v>
@@ -4454,35 +3771,35 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>5.299603939</v>
+        <v>4.354788805</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>5.299603939</v>
+        <v>0.326028805</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -4490,13 +3807,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>4.354788805</v>
+        <v>5.714715481</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -4504,97 +3821,97 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>0.326028805</v>
+        <v>5.714715481</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>5.714715481</v>
+        <v>2.686835045</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.714715481</v>
+        <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>5.714715481</v>
+        <v>11.55922318</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.686835045</v>
+        <v>11.55922318</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1.68004133</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>11.55922318</v>
+        <v>0</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -4602,13 +3919,13 @@
         <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>11.55922318</v>
+        <v>5.395667553</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -4616,13 +3933,13 @@
         <v>14</v>
       </c>
       <c r="B19" t="n">
-        <v>11.55922318</v>
+        <v>5.395667553</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -4630,13 +3947,13 @@
         <v>14</v>
       </c>
       <c r="B20" t="n">
-        <v>1.68004133</v>
+        <v>4.713970695</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -4644,13 +3961,13 @@
         <v>14</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1.592270695</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -4658,10 +3975,10 @@
         <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>5.395667553</v>
+        <v>4.194610119</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
@@ -4672,10 +3989,10 @@
         <v>15</v>
       </c>
       <c r="B23" t="n">
-        <v>5.395667553</v>
+        <v>4.194610119</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4686,10 +4003,10 @@
         <v>15</v>
       </c>
       <c r="B24" t="n">
-        <v>5.395667553</v>
+        <v>4.194610119</v>
       </c>
       <c r="C24" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
@@ -4700,10 +4017,10 @@
         <v>15</v>
       </c>
       <c r="B25" t="n">
-        <v>4.713970695</v>
+        <v>0.979341512</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
@@ -4711,16 +4028,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B26" t="n">
-        <v>1.592270695</v>
+        <v>4.520544529</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -4728,13 +4045,13 @@
         <v>16</v>
       </c>
       <c r="B27" t="n">
-        <v>4.194610119</v>
+        <v>4.520544529</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -4742,13 +4059,13 @@
         <v>16</v>
       </c>
       <c r="B28" t="n">
-        <v>4.194610119</v>
+        <v>3.903719959</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -4756,41 +4073,41 @@
         <v>16</v>
       </c>
       <c r="B29" t="n">
-        <v>4.194610119</v>
+        <v>2.451412267</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B30" t="n">
-        <v>4.194610119</v>
+        <v>5.147699833</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B31" t="n">
-        <v>0.979341512</v>
+        <v>5.147699833</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -4798,13 +4115,13 @@
         <v>17</v>
       </c>
       <c r="B32" t="n">
-        <v>4.520544529</v>
+        <v>2.518207189</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -4812,55 +4129,55 @@
         <v>17</v>
       </c>
       <c r="B33" t="n">
-        <v>4.520544529</v>
+        <v>2.518207189</v>
       </c>
       <c r="C33" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34" t="n">
-        <v>4.520544529</v>
+        <v>4.377658367</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B35" t="n">
-        <v>3.903719959</v>
+        <v>4.377658367</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
       </c>
       <c r="D35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B36" t="n">
-        <v>2.451412267</v>
+        <v>3.45035919</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -4868,77 +4185,77 @@
         <v>18</v>
       </c>
       <c r="B37" t="n">
-        <v>5.147699833</v>
+        <v>1.62445919</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" t="n">
-        <v>5.147699833</v>
+        <v>4.514650345</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" t="n">
-        <v>5.147699833</v>
+        <v>4.514650345</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40" t="n">
-        <v>2.518207189</v>
+        <v>1.77883373</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B41" t="n">
-        <v>2.518207189</v>
+        <v>1.77883373</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B42" t="n">
-        <v>4.377658367</v>
+        <v>5.467858791</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -4949,10 +4266,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B43" t="n">
-        <v>4.377658367</v>
+        <v>5.467858791</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -4963,10 +4280,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44" t="n">
-        <v>4.377658367</v>
+        <v>3.793881119</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -4977,10 +4294,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45" t="n">
-        <v>3.45035919</v>
+        <v>3.793881119</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -4991,237 +4308,237 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B46" t="n">
-        <v>1.62445919</v>
+        <v>5.519124508</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47" t="n">
-        <v>4.514650345</v>
+        <v>5.519124508</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D47" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B48" t="n">
-        <v>4.514650345</v>
+        <v>5.519124508</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D48" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B49" t="n">
-        <v>4.514650345</v>
+        <v>5.519124508</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B50" t="n">
-        <v>1.77883373</v>
+        <v>5.601294994</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B51" t="n">
-        <v>1.77883373</v>
+        <v>5.601294994</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B52" t="n">
-        <v>5.467858791</v>
+        <v>1.826682535</v>
       </c>
       <c r="C52" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B53" t="n">
-        <v>5.467858791</v>
+        <v>0.338682535</v>
       </c>
       <c r="C53" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B54" t="n">
-        <v>5.467858791</v>
+        <v>5.524769306</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
       </c>
       <c r="D54" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B55" t="n">
-        <v>3.793881119</v>
+        <v>5.524769306</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B56" t="n">
-        <v>3.793881119</v>
+        <v>3.660234365</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
       </c>
       <c r="D56" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B57" t="n">
-        <v>5.519124508</v>
+        <v>1.764735466</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
       </c>
       <c r="D57" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B58" t="n">
-        <v>5.519124508</v>
+        <v>4.968757629</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B59" t="n">
-        <v>5.519124508</v>
+        <v>4.968757629</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
       </c>
       <c r="D59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B60" t="n">
-        <v>5.519124508</v>
+        <v>3.733491996</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
       </c>
       <c r="D60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B61" t="n">
-        <v>5.519124508</v>
+        <v>2.319891996</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
       </c>
       <c r="D61" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B62" t="n">
-        <v>5.601294994</v>
+        <v>4.391344547</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D62" t="s">
         <v>6</v>
@@ -5229,13 +4546,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B63" t="n">
-        <v>5.601294994</v>
+        <v>4.391344547</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5243,13 +4560,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B64" t="n">
-        <v>5.601294994</v>
+        <v>4.391344547</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D64" t="s">
         <v>8</v>
@@ -5257,13 +4574,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B65" t="n">
-        <v>1.826682535</v>
+        <v>3.691363053</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D65" t="s">
         <v>9</v>
@@ -5271,237 +4588,237 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B66" t="n">
-        <v>0.338682535</v>
+        <v>4.647268295</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B67" t="n">
-        <v>5.524769306</v>
+        <v>4.647268295</v>
       </c>
       <c r="C67" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B68" t="n">
-        <v>5.524769306</v>
+        <v>2.812137967</v>
       </c>
       <c r="C68" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B69" t="n">
-        <v>5.524769306</v>
+        <v>2.613387967</v>
       </c>
       <c r="C69" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B70" t="n">
-        <v>3.660234365</v>
+        <v>6.180166245</v>
       </c>
       <c r="C70" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B71" t="n">
-        <v>1.764735466</v>
+        <v>6.180166245</v>
       </c>
       <c r="C71" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B72" t="n">
-        <v>4.968757629</v>
+        <v>2.328515997</v>
       </c>
       <c r="C72" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B73" t="n">
-        <v>4.968757629</v>
+        <v>1.584515997</v>
       </c>
       <c r="C73" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B74" t="n">
-        <v>4.968757629</v>
+        <v>4.972505093</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
       </c>
       <c r="D74" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B75" t="n">
-        <v>3.733491996</v>
+        <v>4.972505093</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B76" t="n">
-        <v>2.319891996</v>
+        <v>1.632916742</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B77" t="n">
-        <v>4.391344547</v>
+        <v>0</v>
       </c>
       <c r="C77" t="s">
         <v>5</v>
       </c>
       <c r="D77" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B78" t="n">
-        <v>4.391344547</v>
+        <v>5.185857296</v>
       </c>
       <c r="C78" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B79" t="n">
-        <v>4.391344547</v>
+        <v>5.185857296</v>
       </c>
       <c r="C79" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B80" t="n">
-        <v>4.391344547</v>
+        <v>0.738042031</v>
       </c>
       <c r="C80" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B81" t="n">
-        <v>3.691363053</v>
+        <v>0</v>
       </c>
       <c r="C81" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B82" t="n">
-        <v>4.647268295</v>
+        <v>5.305033207</v>
       </c>
       <c r="C82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D82" t="s">
         <v>6</v>
@@ -5509,13 +4826,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B83" t="n">
-        <v>4.647268295</v>
+        <v>5.305033207</v>
       </c>
       <c r="C83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5523,13 +4840,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B84" t="n">
-        <v>4.647268295</v>
+        <v>2.765415861</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D84" t="s">
         <v>8</v>
@@ -5537,13 +4854,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B85" t="n">
-        <v>2.812137967</v>
+        <v>0</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
@@ -5551,237 +4868,237 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B86" t="n">
-        <v>2.613387967</v>
+        <v>5.672376156</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D86" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B87" t="n">
-        <v>6.180166245</v>
+        <v>5.672376156</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D87" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B88" t="n">
-        <v>6.180166245</v>
+        <v>2.207893405</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D88" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B89" t="n">
-        <v>6.180166245</v>
+        <v>1.569367293</v>
       </c>
       <c r="C89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D89" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B90" t="n">
-        <v>2.328515997</v>
+        <v>9.818370819</v>
       </c>
       <c r="C90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D90" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B91" t="n">
-        <v>1.584515997</v>
+        <v>9.818370819</v>
       </c>
       <c r="C91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B92" t="n">
-        <v>4.972505093</v>
+        <v>3.670291708</v>
       </c>
       <c r="C92" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B93" t="n">
-        <v>4.972505093</v>
+        <v>0</v>
       </c>
       <c r="C93" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B94" t="n">
-        <v>4.972505093</v>
+        <v>10.394557</v>
       </c>
       <c r="C94" t="s">
         <v>5</v>
       </c>
       <c r="D94" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B95" t="n">
-        <v>1.632916742</v>
+        <v>10.394557</v>
       </c>
       <c r="C95" t="s">
         <v>5</v>
       </c>
       <c r="D95" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>2.237728262</v>
       </c>
       <c r="C96" t="s">
         <v>5</v>
       </c>
       <c r="D96" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B97" t="n">
-        <v>5.185857296</v>
+        <v>0</v>
       </c>
       <c r="C97" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D97" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B98" t="n">
-        <v>5.185857296</v>
+        <v>4.827932835</v>
       </c>
       <c r="C98" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D98" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B99" t="n">
-        <v>5.185857296</v>
+        <v>4.827932835</v>
       </c>
       <c r="C99" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D99" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B100" t="n">
-        <v>0.738042031</v>
+        <v>4.162290911</v>
       </c>
       <c r="C100" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>2.277490911</v>
       </c>
       <c r="C101" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D101" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B102" t="n">
-        <v>5.305033207</v>
+        <v>12.69538975</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D102" t="s">
         <v>6</v>
@@ -5789,13 +5106,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B103" t="n">
-        <v>5.305033207</v>
+        <v>12.69538975</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -5803,13 +5120,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B104" t="n">
-        <v>5.305033207</v>
+        <v>1.204466225</v>
       </c>
       <c r="C104" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D104" t="s">
         <v>8</v>
@@ -5817,13 +5134,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B105" t="n">
-        <v>2.765415861</v>
+        <v>0</v>
       </c>
       <c r="C105" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D105" t="s">
         <v>9</v>
@@ -5831,217 +5148,217 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>3.231766701</v>
       </c>
       <c r="C106" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D106" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B107" t="n">
-        <v>5.672376156</v>
+        <v>3.231766701</v>
       </c>
       <c r="C107" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D107" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B108" t="n">
-        <v>5.672376156</v>
+        <v>3.231766701</v>
       </c>
       <c r="C108" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D108" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B109" t="n">
-        <v>5.672376156</v>
+        <v>3.231766701</v>
       </c>
       <c r="C109" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D109" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B110" t="n">
-        <v>2.207893405</v>
+        <v>3.534766912</v>
       </c>
       <c r="C110" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D110" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B111" t="n">
-        <v>1.569367293</v>
+        <v>3.534766912</v>
       </c>
       <c r="C111" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D111" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B112" t="n">
-        <v>9.818370819</v>
+        <v>3.534766912</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D112" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B113" t="n">
-        <v>9.818370819</v>
+        <v>1.111319088</v>
       </c>
       <c r="C113" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B114" t="n">
-        <v>9.818370819</v>
+        <v>19.24587631</v>
       </c>
       <c r="C114" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D114" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B115" t="n">
-        <v>3.670291708</v>
+        <v>19.24587631</v>
       </c>
       <c r="C115" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D115" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>1.326072235</v>
       </c>
       <c r="C116" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D116" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B117" t="n">
-        <v>10.394557</v>
+        <v>0</v>
       </c>
       <c r="C117" t="s">
         <v>5</v>
       </c>
       <c r="D117" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B118" t="n">
-        <v>10.394557</v>
+        <v>17.8643055</v>
       </c>
       <c r="C118" t="s">
         <v>5</v>
       </c>
       <c r="D118" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B119" t="n">
-        <v>10.394557</v>
+        <v>17.8643055</v>
       </c>
       <c r="C119" t="s">
         <v>5</v>
       </c>
       <c r="D119" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B120" t="n">
-        <v>2.237728262</v>
+        <v>1.10944514</v>
       </c>
       <c r="C120" t="s">
         <v>5</v>
       </c>
       <c r="D120" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -6050,18 +5367,18 @@
         <v>5</v>
       </c>
       <c r="D121" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B122" t="n">
-        <v>4.827932835</v>
+        <v>4.148550987</v>
       </c>
       <c r="C122" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D122" t="s">
         <v>6</v>
@@ -6069,13 +5386,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B123" t="n">
-        <v>4.827932835</v>
+        <v>4.148550987</v>
       </c>
       <c r="C123" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6083,13 +5400,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B124" t="n">
-        <v>4.827932835</v>
+        <v>4.148550987</v>
       </c>
       <c r="C124" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
@@ -6097,13 +5414,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B125" t="n">
-        <v>4.162290911</v>
+        <v>4.065119763</v>
       </c>
       <c r="C125" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
@@ -6111,234 +5428,234 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B126" t="n">
-        <v>2.277490911</v>
+        <v>2.685848951</v>
       </c>
       <c r="C126" t="s">
         <v>5</v>
       </c>
       <c r="D126" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B127" t="n">
-        <v>12.69538975</v>
+        <v>2.685848951</v>
       </c>
       <c r="C127" t="s">
         <v>5</v>
       </c>
       <c r="D127" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B128" t="n">
-        <v>12.69538975</v>
+        <v>1.931165606</v>
       </c>
       <c r="C128" t="s">
         <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B129" t="n">
-        <v>12.69538975</v>
+        <v>1.931165606</v>
       </c>
       <c r="C129" t="s">
         <v>5</v>
       </c>
       <c r="D129" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B130" t="n">
-        <v>1.204466225</v>
+        <v>4.167097569</v>
       </c>
       <c r="C130" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D130" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>4.167097569</v>
       </c>
       <c r="C131" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D131" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B132" t="n">
-        <v>3.231766701</v>
+        <v>4.167097569</v>
       </c>
       <c r="C132" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D132" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B133" t="n">
-        <v>3.231766701</v>
+        <v>4.052287413</v>
       </c>
       <c r="C133" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D133" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B134" t="n">
-        <v>3.231766701</v>
+        <v>2.809998035</v>
       </c>
       <c r="C134" t="s">
         <v>5</v>
       </c>
       <c r="D134" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B135" t="n">
-        <v>3.231766701</v>
+        <v>2.809998035</v>
       </c>
       <c r="C135" t="s">
         <v>5</v>
       </c>
       <c r="D135" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B136" t="n">
-        <v>3.231766701</v>
+        <v>2.809998035</v>
       </c>
       <c r="C136" t="s">
         <v>5</v>
       </c>
       <c r="D136" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B137" t="n">
-        <v>3.534766912</v>
+        <v>1.014136333</v>
       </c>
       <c r="C137" t="s">
         <v>5</v>
       </c>
       <c r="D137" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B138" t="n">
-        <v>3.534766912</v>
+        <v>2.873369217</v>
       </c>
       <c r="C138" t="s">
         <v>5</v>
       </c>
       <c r="D138" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B139" t="n">
-        <v>3.534766912</v>
+        <v>2.873369217</v>
       </c>
       <c r="C139" t="s">
         <v>5</v>
       </c>
       <c r="D139" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B140" t="n">
-        <v>3.534766912</v>
+        <v>2.873369217</v>
       </c>
       <c r="C140" t="s">
         <v>5</v>
       </c>
       <c r="D140" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B141" t="n">
-        <v>1.111319088</v>
+        <v>2.873369217</v>
       </c>
       <c r="C141" t="s">
         <v>5</v>
       </c>
       <c r="D141" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B142" t="n">
-        <v>19.24587631</v>
+        <v>4.041529655</v>
       </c>
       <c r="C142" t="s">
         <v>5</v>
@@ -6349,10 +5666,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B143" t="n">
-        <v>19.24587631</v>
+        <v>4.041529655</v>
       </c>
       <c r="C143" t="s">
         <v>5</v>
@@ -6363,10 +5680,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B144" t="n">
-        <v>19.24587631</v>
+        <v>2.155314104</v>
       </c>
       <c r="C144" t="s">
         <v>5</v>
@@ -6377,10 +5694,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B145" t="n">
-        <v>1.326072235</v>
+        <v>1.860814104</v>
       </c>
       <c r="C145" t="s">
         <v>5</v>
@@ -6391,237 +5708,237 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>2.830694914</v>
       </c>
       <c r="C146" t="s">
         <v>5</v>
       </c>
       <c r="D146" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B147" t="n">
-        <v>17.8643055</v>
+        <v>2.830694914</v>
       </c>
       <c r="C147" t="s">
         <v>5</v>
       </c>
       <c r="D147" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B148" t="n">
-        <v>17.8643055</v>
+        <v>2.830694914</v>
       </c>
       <c r="C148" t="s">
         <v>5</v>
       </c>
       <c r="D148" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B149" t="n">
-        <v>17.8643055</v>
+        <v>1.993018749</v>
       </c>
       <c r="C149" t="s">
         <v>5</v>
       </c>
       <c r="D149" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B150" t="n">
-        <v>1.10944514</v>
+        <v>2.128945351</v>
       </c>
       <c r="C150" t="s">
         <v>5</v>
       </c>
       <c r="D150" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>2.128945351</v>
       </c>
       <c r="C151" t="s">
         <v>5</v>
       </c>
       <c r="D151" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B152" t="n">
-        <v>4.148550987</v>
+        <v>2.128945351</v>
       </c>
       <c r="C152" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D152" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B153" t="n">
-        <v>4.148550987</v>
+        <v>1.954484833</v>
       </c>
       <c r="C153" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D153" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B154" t="n">
-        <v>4.148550987</v>
+        <v>5.529391289</v>
       </c>
       <c r="C154" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D154" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B155" t="n">
-        <v>4.148550987</v>
+        <v>5.529391289</v>
       </c>
       <c r="C155" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D155" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B156" t="n">
-        <v>4.065119763</v>
+        <v>3.445126061</v>
       </c>
       <c r="C156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D156" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B157" t="n">
-        <v>2.685848951</v>
+        <v>2.887126061</v>
       </c>
       <c r="C157" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D157" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B158" t="n">
-        <v>2.685848951</v>
+        <v>3.190342426</v>
       </c>
       <c r="C158" t="s">
         <v>5</v>
       </c>
       <c r="D158" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B159" t="n">
-        <v>2.685848951</v>
+        <v>3.190342426</v>
       </c>
       <c r="C159" t="s">
         <v>5</v>
       </c>
       <c r="D159" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B160" t="n">
-        <v>1.931165606</v>
+        <v>3.190342426</v>
       </c>
       <c r="C160" t="s">
         <v>5</v>
       </c>
       <c r="D160" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B161" t="n">
-        <v>1.931165606</v>
+        <v>0.854185474</v>
       </c>
       <c r="C161" t="s">
         <v>5</v>
       </c>
       <c r="D161" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B162" t="n">
-        <v>4.167097569</v>
+        <v>3.32204628</v>
       </c>
       <c r="C162" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D162" t="s">
         <v>6</v>
@@ -6629,13 +5946,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B163" t="n">
-        <v>4.167097569</v>
+        <v>3.32204628</v>
       </c>
       <c r="C163" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -6643,13 +5960,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B164" t="n">
-        <v>4.167097569</v>
+        <v>1.885301766</v>
       </c>
       <c r="C164" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D164" t="s">
         <v>8</v>
@@ -6657,13 +5974,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B165" t="n">
-        <v>4.167097569</v>
+        <v>0.000501766</v>
       </c>
       <c r="C165" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
@@ -6671,237 +5988,237 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B166" t="n">
-        <v>4.052287413</v>
+        <v>3.305774689</v>
       </c>
       <c r="C166" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D166" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B167" t="n">
-        <v>2.809998035</v>
+        <v>3.305774689</v>
       </c>
       <c r="C167" t="s">
         <v>5</v>
       </c>
       <c r="D167" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B168" t="n">
-        <v>2.809998035</v>
+        <v>3.305774689</v>
       </c>
       <c r="C168" t="s">
         <v>5</v>
       </c>
       <c r="D168" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B169" t="n">
-        <v>2.809998035</v>
+        <v>3.305774689</v>
       </c>
       <c r="C169" t="s">
         <v>5</v>
       </c>
       <c r="D169" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B170" t="n">
-        <v>2.809998035</v>
+        <v>3.033854961</v>
       </c>
       <c r="C170" t="s">
         <v>5</v>
       </c>
       <c r="D170" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B171" t="n">
-        <v>1.014136333</v>
+        <v>3.033854961</v>
       </c>
       <c r="C171" t="s">
         <v>5</v>
       </c>
       <c r="D171" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B172" t="n">
-        <v>2.873369217</v>
+        <v>3.033854961</v>
       </c>
       <c r="C172" t="s">
         <v>5</v>
       </c>
       <c r="D172" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B173" t="n">
-        <v>2.873369217</v>
+        <v>2.15854252</v>
       </c>
       <c r="C173" t="s">
         <v>5</v>
       </c>
       <c r="D173" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B174" t="n">
-        <v>2.873369217</v>
+        <v>3.242710829</v>
       </c>
       <c r="C174" t="s">
         <v>5</v>
       </c>
       <c r="D174" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B175" t="n">
-        <v>2.873369217</v>
+        <v>3.242710829</v>
       </c>
       <c r="C175" t="s">
         <v>5</v>
       </c>
       <c r="D175" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B176" t="n">
-        <v>2.873369217</v>
+        <v>3.242710829</v>
       </c>
       <c r="C176" t="s">
         <v>5</v>
       </c>
       <c r="D176" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B177" t="n">
-        <v>4.041529655</v>
+        <v>2.873608972</v>
       </c>
       <c r="C177" t="s">
         <v>5</v>
       </c>
       <c r="D177" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B178" t="n">
-        <v>4.041529655</v>
+        <v>3.275354624</v>
       </c>
       <c r="C178" t="s">
         <v>5</v>
       </c>
       <c r="D178" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B179" t="n">
-        <v>4.041529655</v>
+        <v>3.275354624</v>
       </c>
       <c r="C179" t="s">
         <v>5</v>
       </c>
       <c r="D179" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B180" t="n">
-        <v>2.155314104</v>
+        <v>3.275354624</v>
       </c>
       <c r="C180" t="s">
         <v>5</v>
       </c>
       <c r="D180" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B181" t="n">
-        <v>1.860814104</v>
+        <v>1.712926049</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
       </c>
       <c r="D181" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B182" t="n">
-        <v>2.830694914</v>
+        <v>4.54736948</v>
       </c>
       <c r="C182" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D182" t="s">
         <v>6</v>
@@ -6909,13 +6226,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B183" t="n">
-        <v>2.830694914</v>
+        <v>4.54736948</v>
       </c>
       <c r="C183" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -6923,13 +6240,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B184" t="n">
-        <v>2.830694914</v>
+        <v>2.210310245</v>
       </c>
       <c r="C184" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D184" t="s">
         <v>8</v>
@@ -6937,13 +6254,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B185" t="n">
-        <v>2.830694914</v>
+        <v>0</v>
       </c>
       <c r="C185" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D185" t="s">
         <v>9</v>
@@ -6951,237 +6268,237 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B186" t="n">
-        <v>1.993018749</v>
+        <v>3.558572054</v>
       </c>
       <c r="C186" t="s">
         <v>5</v>
       </c>
       <c r="D186" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B187" t="n">
-        <v>2.128945351</v>
+        <v>3.558572054</v>
       </c>
       <c r="C187" t="s">
         <v>5</v>
       </c>
       <c r="D187" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B188" t="n">
-        <v>2.128945351</v>
+        <v>3.558572054</v>
       </c>
       <c r="C188" t="s">
         <v>5</v>
       </c>
       <c r="D188" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B189" t="n">
-        <v>2.128945351</v>
+        <v>3.558572054</v>
       </c>
       <c r="C189" t="s">
         <v>5</v>
       </c>
       <c r="D189" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B190" t="n">
-        <v>2.128945351</v>
+        <v>3.269914865</v>
       </c>
       <c r="C190" t="s">
         <v>5</v>
       </c>
       <c r="D190" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B191" t="n">
-        <v>1.954484833</v>
+        <v>3.269914865</v>
       </c>
       <c r="C191" t="s">
         <v>5</v>
       </c>
       <c r="D191" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B192" t="n">
-        <v>5.529391289</v>
+        <v>3.2151662</v>
       </c>
       <c r="C192" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D192" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B193" t="n">
-        <v>5.529391289</v>
+        <v>3.2151662</v>
       </c>
       <c r="C193" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D193" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B194" t="n">
-        <v>5.529391289</v>
+        <v>3.302062273</v>
       </c>
       <c r="C194" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D194" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B195" t="n">
-        <v>3.445126061</v>
+        <v>3.302062273</v>
       </c>
       <c r="C195" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D195" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B196" t="n">
-        <v>2.887126061</v>
+        <v>3.302062273</v>
       </c>
       <c r="C196" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D196" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B197" t="n">
-        <v>3.190342426</v>
+        <v>2.425104612</v>
       </c>
       <c r="C197" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D197" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B198" t="n">
-        <v>3.190342426</v>
+        <v>3.201862574</v>
       </c>
       <c r="C198" t="s">
         <v>5</v>
       </c>
       <c r="D198" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B199" t="n">
-        <v>3.190342426</v>
+        <v>3.201862574</v>
       </c>
       <c r="C199" t="s">
         <v>5</v>
       </c>
       <c r="D199" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B200" t="n">
-        <v>3.190342426</v>
+        <v>3.201862574</v>
       </c>
       <c r="C200" t="s">
         <v>5</v>
       </c>
       <c r="D200" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B201" t="n">
-        <v>0.854185474</v>
+        <v>2.910055472</v>
       </c>
       <c r="C201" t="s">
         <v>5</v>
       </c>
       <c r="D201" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B202" t="n">
-        <v>3.32204628</v>
+        <v>2.237344503</v>
       </c>
       <c r="C202" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D202" t="s">
         <v>6</v>
@@ -7189,13 +6506,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B203" t="n">
-        <v>3.32204628</v>
+        <v>2.237344503</v>
       </c>
       <c r="C203" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7203,13 +6520,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B204" t="n">
-        <v>3.32204628</v>
+        <v>2.237344503</v>
       </c>
       <c r="C204" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D204" t="s">
         <v>8</v>
@@ -7217,13 +6534,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B205" t="n">
-        <v>1.885301766</v>
+        <v>2.237344503</v>
       </c>
       <c r="C205" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D205" t="s">
         <v>9</v>
@@ -7231,856 +6548,114 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B206" t="n">
-        <v>0.000501766</v>
+        <v>3.489558458</v>
       </c>
       <c r="C206" t="s">
         <v>5</v>
       </c>
       <c r="D206" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B207" t="n">
-        <v>3.305774689</v>
+        <v>3.489558458</v>
       </c>
       <c r="C207" t="s">
         <v>5</v>
       </c>
       <c r="D207" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B208" t="n">
-        <v>3.305774689</v>
+        <v>1.885925644</v>
       </c>
       <c r="C208" t="s">
         <v>5</v>
       </c>
       <c r="D208" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B209" t="n">
-        <v>3.305774689</v>
+        <v>0</v>
       </c>
       <c r="C209" t="s">
         <v>5</v>
       </c>
       <c r="D209" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B210" t="n">
-        <v>3.305774689</v>
+        <v>3.724695683</v>
       </c>
       <c r="C210" t="s">
         <v>5</v>
       </c>
       <c r="D210" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B211" t="n">
-        <v>3.305774689</v>
+        <v>3.724695683</v>
       </c>
       <c r="C211" t="s">
         <v>5</v>
       </c>
       <c r="D211" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B212" t="n">
-        <v>3.033854961</v>
+        <v>2.700863073</v>
       </c>
       <c r="C212" t="s">
         <v>5</v>
       </c>
       <c r="D212" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B213" t="n">
-        <v>3.033854961</v>
+        <v>0.285963073</v>
       </c>
       <c r="C213" t="s">
         <v>5</v>
       </c>
       <c r="D213" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="s">
-        <v>53</v>
-      </c>
-      <c r="B214" t="n">
-        <v>3.033854961</v>
-      </c>
-      <c r="C214" t="s">
-        <v>5</v>
-      </c>
-      <c r="D214" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="s">
-        <v>53</v>
-      </c>
-      <c r="B215" t="n">
-        <v>3.033854961</v>
-      </c>
-      <c r="C215" t="s">
-        <v>5</v>
-      </c>
-      <c r="D215" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="s">
-        <v>53</v>
-      </c>
-      <c r="B216" t="n">
-        <v>2.15854252</v>
-      </c>
-      <c r="C216" t="s">
-        <v>5</v>
-      </c>
-      <c r="D216" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="s">
-        <v>54</v>
-      </c>
-      <c r="B217" t="n">
-        <v>3.242710829</v>
-      </c>
-      <c r="C217" t="s">
-        <v>5</v>
-      </c>
-      <c r="D217" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="s">
-        <v>54</v>
-      </c>
-      <c r="B218" t="n">
-        <v>3.242710829</v>
-      </c>
-      <c r="C218" t="s">
-        <v>5</v>
-      </c>
-      <c r="D218" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="s">
-        <v>54</v>
-      </c>
-      <c r="B219" t="n">
-        <v>3.242710829</v>
-      </c>
-      <c r="C219" t="s">
-        <v>5</v>
-      </c>
-      <c r="D219" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="s">
-        <v>54</v>
-      </c>
-      <c r="B220" t="n">
-        <v>3.242710829</v>
-      </c>
-      <c r="C220" t="s">
-        <v>5</v>
-      </c>
-      <c r="D220" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="s">
-        <v>54</v>
-      </c>
-      <c r="B221" t="n">
-        <v>2.873608972</v>
-      </c>
-      <c r="C221" t="s">
-        <v>5</v>
-      </c>
-      <c r="D221" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="s">
-        <v>55</v>
-      </c>
-      <c r="B222" t="n">
-        <v>3.275354624</v>
-      </c>
-      <c r="C222" t="s">
-        <v>5</v>
-      </c>
-      <c r="D222" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="s">
-        <v>55</v>
-      </c>
-      <c r="B223" t="n">
-        <v>3.275354624</v>
-      </c>
-      <c r="C223" t="s">
-        <v>5</v>
-      </c>
-      <c r="D223" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="s">
-        <v>55</v>
-      </c>
-      <c r="B224" t="n">
-        <v>3.275354624</v>
-      </c>
-      <c r="C224" t="s">
-        <v>5</v>
-      </c>
-      <c r="D224" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="s">
-        <v>55</v>
-      </c>
-      <c r="B225" t="n">
-        <v>3.275354624</v>
-      </c>
-      <c r="C225" t="s">
-        <v>5</v>
-      </c>
-      <c r="D225" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="s">
-        <v>55</v>
-      </c>
-      <c r="B226" t="n">
-        <v>1.712926049</v>
-      </c>
-      <c r="C226" t="s">
-        <v>5</v>
-      </c>
-      <c r="D226" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s">
-        <v>56</v>
-      </c>
-      <c r="B227" t="n">
-        <v>4.54736948</v>
-      </c>
-      <c r="C227" t="s">
-        <v>13</v>
-      </c>
-      <c r="D227" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="s">
-        <v>56</v>
-      </c>
-      <c r="B228" t="n">
-        <v>4.54736948</v>
-      </c>
-      <c r="C228" t="s">
-        <v>13</v>
-      </c>
-      <c r="D228" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="s">
-        <v>56</v>
-      </c>
-      <c r="B229" t="n">
-        <v>4.54736948</v>
-      </c>
-      <c r="C229" t="s">
-        <v>13</v>
-      </c>
-      <c r="D229" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="s">
-        <v>56</v>
-      </c>
-      <c r="B230" t="n">
-        <v>2.210310245</v>
-      </c>
-      <c r="C230" t="s">
-        <v>13</v>
-      </c>
-      <c r="D230" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="s">
-        <v>56</v>
-      </c>
-      <c r="B231" t="n">
-        <v>0</v>
-      </c>
-      <c r="C231" t="s">
-        <v>13</v>
-      </c>
-      <c r="D231" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="s">
-        <v>57</v>
-      </c>
-      <c r="B232" t="n">
-        <v>3.558572054</v>
-      </c>
-      <c r="C232" t="s">
-        <v>5</v>
-      </c>
-      <c r="D232" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="s">
-        <v>57</v>
-      </c>
-      <c r="B233" t="n">
-        <v>3.558572054</v>
-      </c>
-      <c r="C233" t="s">
-        <v>5</v>
-      </c>
-      <c r="D233" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="s">
-        <v>57</v>
-      </c>
-      <c r="B234" t="n">
-        <v>3.558572054</v>
-      </c>
-      <c r="C234" t="s">
-        <v>5</v>
-      </c>
-      <c r="D234" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="s">
-        <v>57</v>
-      </c>
-      <c r="B235" t="n">
-        <v>3.558572054</v>
-      </c>
-      <c r="C235" t="s">
-        <v>5</v>
-      </c>
-      <c r="D235" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="s">
-        <v>57</v>
-      </c>
-      <c r="B236" t="n">
-        <v>3.558572054</v>
-      </c>
-      <c r="C236" t="s">
-        <v>5</v>
-      </c>
-      <c r="D236" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="s">
-        <v>58</v>
-      </c>
-      <c r="B237" t="n">
-        <v>3.269914865</v>
-      </c>
-      <c r="C237" t="s">
-        <v>5</v>
-      </c>
-      <c r="D237" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="s">
-        <v>58</v>
-      </c>
-      <c r="B238" t="n">
-        <v>3.269914865</v>
-      </c>
-      <c r="C238" t="s">
-        <v>5</v>
-      </c>
-      <c r="D238" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="s">
-        <v>58</v>
-      </c>
-      <c r="B239" t="n">
-        <v>3.269914865</v>
-      </c>
-      <c r="C239" t="s">
-        <v>5</v>
-      </c>
-      <c r="D239" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="s">
-        <v>58</v>
-      </c>
-      <c r="B240" t="n">
-        <v>3.2151662</v>
-      </c>
-      <c r="C240" t="s">
-        <v>5</v>
-      </c>
-      <c r="D240" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="s">
-        <v>58</v>
-      </c>
-      <c r="B241" t="n">
-        <v>3.2151662</v>
-      </c>
-      <c r="C241" t="s">
-        <v>5</v>
-      </c>
-      <c r="D241" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s">
-        <v>59</v>
-      </c>
-      <c r="B242" t="n">
-        <v>3.302062273</v>
-      </c>
-      <c r="C242" t="s">
-        <v>13</v>
-      </c>
-      <c r="D242" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s">
-        <v>59</v>
-      </c>
-      <c r="B243" t="n">
-        <v>3.302062273</v>
-      </c>
-      <c r="C243" t="s">
-        <v>13</v>
-      </c>
-      <c r="D243" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s">
-        <v>59</v>
-      </c>
-      <c r="B244" t="n">
-        <v>3.302062273</v>
-      </c>
-      <c r="C244" t="s">
-        <v>13</v>
-      </c>
-      <c r="D244" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="s">
-        <v>59</v>
-      </c>
-      <c r="B245" t="n">
-        <v>3.302062273</v>
-      </c>
-      <c r="C245" t="s">
-        <v>13</v>
-      </c>
-      <c r="D245" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="s">
-        <v>59</v>
-      </c>
-      <c r="B246" t="n">
-        <v>2.425104612</v>
-      </c>
-      <c r="C246" t="s">
-        <v>13</v>
-      </c>
-      <c r="D246" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="s">
-        <v>60</v>
-      </c>
-      <c r="B247" t="n">
-        <v>3.201862574</v>
-      </c>
-      <c r="C247" t="s">
-        <v>5</v>
-      </c>
-      <c r="D247" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="s">
-        <v>60</v>
-      </c>
-      <c r="B248" t="n">
-        <v>3.201862574</v>
-      </c>
-      <c r="C248" t="s">
-        <v>5</v>
-      </c>
-      <c r="D248" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s">
-        <v>60</v>
-      </c>
-      <c r="B249" t="n">
-        <v>3.201862574</v>
-      </c>
-      <c r="C249" t="s">
-        <v>5</v>
-      </c>
-      <c r="D249" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="s">
-        <v>60</v>
-      </c>
-      <c r="B250" t="n">
-        <v>3.201862574</v>
-      </c>
-      <c r="C250" t="s">
-        <v>5</v>
-      </c>
-      <c r="D250" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="s">
-        <v>60</v>
-      </c>
-      <c r="B251" t="n">
-        <v>2.910055472</v>
-      </c>
-      <c r="C251" t="s">
-        <v>5</v>
-      </c>
-      <c r="D251" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="s">
-        <v>61</v>
-      </c>
-      <c r="B252" t="n">
-        <v>2.237344503</v>
-      </c>
-      <c r="C252" t="s">
-        <v>13</v>
-      </c>
-      <c r="D252" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="s">
-        <v>61</v>
-      </c>
-      <c r="B253" t="n">
-        <v>2.237344503</v>
-      </c>
-      <c r="C253" t="s">
-        <v>13</v>
-      </c>
-      <c r="D253" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s">
-        <v>61</v>
-      </c>
-      <c r="B254" t="n">
-        <v>2.237344503</v>
-      </c>
-      <c r="C254" t="s">
-        <v>13</v>
-      </c>
-      <c r="D254" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="s">
-        <v>61</v>
-      </c>
-      <c r="B255" t="n">
-        <v>2.237344503</v>
-      </c>
-      <c r="C255" t="s">
-        <v>13</v>
-      </c>
-      <c r="D255" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="s">
-        <v>61</v>
-      </c>
-      <c r="B256" t="n">
-        <v>2.237344503</v>
-      </c>
-      <c r="C256" t="s">
-        <v>13</v>
-      </c>
-      <c r="D256" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="s">
-        <v>62</v>
-      </c>
-      <c r="B257" t="n">
-        <v>3.489558458</v>
-      </c>
-      <c r="C257" t="s">
-        <v>5</v>
-      </c>
-      <c r="D257" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="s">
-        <v>62</v>
-      </c>
-      <c r="B258" t="n">
-        <v>3.489558458</v>
-      </c>
-      <c r="C258" t="s">
-        <v>5</v>
-      </c>
-      <c r="D258" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="s">
-        <v>62</v>
-      </c>
-      <c r="B259" t="n">
-        <v>3.489558458</v>
-      </c>
-      <c r="C259" t="s">
-        <v>5</v>
-      </c>
-      <c r="D259" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>62</v>
-      </c>
-      <c r="B260" t="n">
-        <v>1.885925644</v>
-      </c>
-      <c r="C260" t="s">
-        <v>5</v>
-      </c>
-      <c r="D260" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="s">
-        <v>62</v>
-      </c>
-      <c r="B261" t="n">
-        <v>0</v>
-      </c>
-      <c r="C261" t="s">
-        <v>5</v>
-      </c>
-      <c r="D261" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="s">
-        <v>63</v>
-      </c>
-      <c r="B262" t="n">
-        <v>3.724695683</v>
-      </c>
-      <c r="C262" t="s">
-        <v>5</v>
-      </c>
-      <c r="D262" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="s">
-        <v>63</v>
-      </c>
-      <c r="B263" t="n">
-        <v>3.724695683</v>
-      </c>
-      <c r="C263" t="s">
-        <v>5</v>
-      </c>
-      <c r="D263" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="s">
-        <v>63</v>
-      </c>
-      <c r="B264" t="n">
-        <v>3.724695683</v>
-      </c>
-      <c r="C264" t="s">
-        <v>5</v>
-      </c>
-      <c r="D264" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="s">
-        <v>63</v>
-      </c>
-      <c r="B265" t="n">
-        <v>2.700863073</v>
-      </c>
-      <c r="C265" t="s">
-        <v>5</v>
-      </c>
-      <c r="D265" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="s">
-        <v>63</v>
-      </c>
-      <c r="B266" t="n">
-        <v>0.285963073</v>
-      </c>
-      <c r="C266" t="s">
-        <v>5</v>
-      </c>
-      <c r="D266" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8096,68 +6671,128 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>5.23772737681132</v>
+        <v>5.32460255777778</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>5.23772737681132</v>
+        <v>5.32460255777778</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.564841975940555</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>2.93037891130189</v>
+        <v>5.32460255777778</v>
       </c>
       <c r="C4" t="n">
-        <v>0.559475264840125</v>
+        <v>0.324520981378403</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>1.68406316009434</v>
+        <v>5.32460255777778</v>
       </c>
       <c r="C5" t="n">
-        <v>0.321525547043569</v>
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>5.23772737681132</v>
+        <v>5.05375640535294</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5.05375640535294</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.547501390720648</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5.05375640535294</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.314842319087515</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5.05375640535294</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
